--- a/MINI_models.xlsx
+++ b/MINI_models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MINI 트랜스폰더 DB'!$A$1:$P$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MINI 트랜스폰더 DB'!$A$1:$P$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P90"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O36" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 다나와(컨버터블 F57 2016.4 국내 출시)</t>
         </is>
       </c>
       <c r="P36" s="9" t="inlineStr"/>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="O37" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 다나와(컨버터블 F57 2016.4 국내 출시)</t>
         </is>
       </c>
       <c r="P37" s="9" t="inlineStr"/>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="O38" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 다나와(컨버터블 F57 2016.4 국내 출시)</t>
         </is>
       </c>
       <c r="P38" s="9" t="inlineStr"/>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -3236,7 +3236,7 @@
       <c r="K39" s="9" t="inlineStr"/>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>66128781934</t>
+          <t>66128781934, 66128728017[컴포트 액세스]</t>
         </is>
       </c>
       <c r="M39" s="9" t="inlineStr"/>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O39" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 다나와(컨버터블 F57 2016.4 국내 출시)</t>
         </is>
       </c>
       <c r="P39" s="9" t="inlineStr"/>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="O40" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 다나와(컨버터블 F57 2016.4 국내 출시)</t>
         </is>
       </c>
       <c r="P40" s="9" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="O41" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 다나와(컨버터블 F57 2016.4 국내 출시)</t>
         </is>
       </c>
       <c r="P41" s="9" t="inlineStr"/>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="O42" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 다나와(컨버터블 F57 2016.4 국내 출시)</t>
         </is>
       </c>
       <c r="P42" s="9" t="inlineStr"/>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O43" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 다나와(컨버터블 F57 2016.4 국내 출시)</t>
         </is>
       </c>
       <c r="P43" s="9" t="inlineStr"/>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024(단종)</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="O44" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 다나와(컨버터블 F57 2016.4 국내 출시)</t>
         </is>
       </c>
       <c r="P44" s="9" t="inlineStr"/>
@@ -3610,22 +3610,22 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>컨버터블 (F57, 3세대)</t>
+          <t>쿠페/로드스터 (R58/R59)</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>2024(단종)</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>ID49(PCF7953P)</t>
+          <t>ID46(PCF7945)</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
@@ -3645,29 +3645,29 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>51217359252[비상키, 해외 공용 품번]</t>
+          <t>51212756065[비상키, 해외 공용 품번], 51212756061[비상키, 해외 공용 품번], 66123456377[트랜스폰더 키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>HU100R</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K45" s="9" t="inlineStr"/>
       <c r="L45" s="9" t="inlineStr">
         <is>
-          <t>66128781934, 66128728017[컴포트 액세스]</t>
+          <t>66123456369, 66123456373[컴포트 액세스]</t>
         </is>
       </c>
       <c r="M45" s="9" t="inlineStr"/>
       <c r="N45" s="9" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>CAS3, CAS3+</t>
         </is>
       </c>
       <c r="O45" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F57 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI R58·R59 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), 머니투데이·이데일리(MINI 로드스터 2012.4.24 국내 출시)</t>
         </is>
       </c>
       <c r="P45" s="9" t="inlineStr"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="O46" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R58·R59 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI R58·R59 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), 머니투데이·이데일리(MINI 로드스터 2012.4.24 국내 출시)</t>
         </is>
       </c>
       <c r="P46" s="9" t="inlineStr"/>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="O47" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R58·R59 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI R58·R59 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), 머니투데이·이데일리(MINI 로드스터 2012.4.24 국내 출시)</t>
         </is>
       </c>
       <c r="P47" s="9" t="inlineStr"/>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2015(단종)</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="O48" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R58·R59 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI R58·R59 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), 머니투데이·이데일리(MINI 로드스터 2012.4.24 국내 출시)</t>
         </is>
       </c>
       <c r="P48" s="9" t="inlineStr"/>
@@ -3890,12 +3890,12 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>쿠페/로드스터 (R58/R59)</t>
+          <t>클럽맨 (R55, 2세대)</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>2015(단종)</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="O49" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R58·R59 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), BMW 그룹 코리아 보도자료(MINI 클럽맨 2008.2.26 국내 첫 출시)</t>
         </is>
       </c>
       <c r="P49" s="9" t="inlineStr"/>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="O50" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), BMW 그룹 코리아 보도자료(MINI 클럽맨 2008.2.26 국내 첫 출시)</t>
         </is>
       </c>
       <c r="P50" s="9" t="inlineStr"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="O51" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), BMW 그룹 코리아 보도자료(MINI 클럽맨 2008.2.26 국내 첫 출시)</t>
         </is>
       </c>
       <c r="P51" s="9" t="inlineStr"/>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="O52" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), BMW 그룹 코리아 보도자료(MINI 클럽맨 2008.2.26 국내 첫 출시)</t>
         </is>
       </c>
       <c r="P52" s="9" t="inlineStr"/>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O53" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), BMW 그룹 코리아 보도자료(MINI 클럽맨 2008.2.26 국내 첫 출시)</t>
         </is>
       </c>
       <c r="P53" s="9" t="inlineStr"/>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="O54" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), BMW 그룹 코리아 보도자료(MINI 클럽맨 2008.2.26 국내 첫 출시)</t>
         </is>
       </c>
       <c r="P54" s="9" t="inlineStr"/>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="O55" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), BMW 그룹 코리아 보도자료(MINI 클럽맨 2008.2.26 국내 첫 출시)</t>
         </is>
       </c>
       <c r="P55" s="9" t="inlineStr"/>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2015(단종)</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O56" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), BMW 그룹 코리아 보도자료(MINI 클럽맨 2008.2.26 국내 첫 출시)</t>
         </is>
       </c>
       <c r="P56" s="9" t="inlineStr"/>
@@ -4450,22 +4450,22 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>클럽맨 (R55, 2세대)</t>
+          <t>클럽맨 (F54, 3세대)</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>ID46(PCF7945)</t>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
@@ -4485,29 +4485,29 @@
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>51212756065[비상키, 해외 공용 품번], 51212756061[비상키, 해외 공용 품번], 66123456377[트랜스폰더 키, 해외 공용 품번]</t>
+          <t>51217359252[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K57" s="9" t="inlineStr"/>
       <c r="L57" s="9" t="inlineStr">
         <is>
-          <t>66123456369, 66123456373[컴포트 액세스]</t>
+          <t>66128781934</t>
         </is>
       </c>
       <c r="M57" s="9" t="inlineStr"/>
       <c r="N57" s="9" t="inlineStr">
         <is>
-          <t>CAS3, CAS3+</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O57" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 서울신문(뉴 MINI 클럽맨 2015.11.20 국내 출시)</t>
         </is>
       </c>
       <c r="P57" s="9" t="inlineStr"/>
@@ -4520,22 +4520,22 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>클럽맨 (R55, 2세대)</t>
+          <t>클럽맨 (F54, 3세대)</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>2015(단종)</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>ID46(PCF7945)</t>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
@@ -4555,29 +4555,29 @@
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>51212756065[비상키, 해외 공용 품번], 51212756061[비상키, 해외 공용 품번], 66123456377[트랜스폰더 키, 해외 공용 품번]</t>
+          <t>51217359252[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr"/>
       <c r="L58" s="9" t="inlineStr">
         <is>
-          <t>66123456369, 66123456373[컴포트 액세스]</t>
+          <t>66128781934</t>
         </is>
       </c>
       <c r="M58" s="9" t="inlineStr"/>
       <c r="N58" s="9" t="inlineStr">
         <is>
-          <t>CAS3, CAS3+</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O58" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R55·R55N 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 서울신문(뉴 MINI 클럽맨 2015.11.20 국내 출시)</t>
         </is>
       </c>
       <c r="P58" s="9" t="inlineStr"/>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="O59" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 서울신문(뉴 MINI 클럽맨 2015.11.20 국내 출시)</t>
         </is>
       </c>
       <c r="P59" s="9" t="inlineStr"/>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="O60" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 서울신문(뉴 MINI 클럽맨 2015.11.20 국내 출시)</t>
         </is>
       </c>
       <c r="P60" s="9" t="inlineStr"/>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -4776,7 +4776,7 @@
       <c r="K61" s="9" t="inlineStr"/>
       <c r="L61" s="9" t="inlineStr">
         <is>
-          <t>66128781934</t>
+          <t>66128781934, 66128728017[컴포트 액세스]</t>
         </is>
       </c>
       <c r="M61" s="9" t="inlineStr"/>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O61" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 서울신문(뉴 MINI 클럽맨 2015.11.20 국내 출시)</t>
         </is>
       </c>
       <c r="P61" s="9" t="inlineStr"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -4846,7 +4846,7 @@
       <c r="K62" s="9" t="inlineStr"/>
       <c r="L62" s="9" t="inlineStr">
         <is>
-          <t>66128781934</t>
+          <t>66128781934, 66128728017[컴포트 액세스]</t>
         </is>
       </c>
       <c r="M62" s="9" t="inlineStr"/>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="O62" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 서울신문(뉴 MINI 클럽맨 2015.11.20 국내 출시)</t>
         </is>
       </c>
       <c r="P62" s="9" t="inlineStr"/>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="O63" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 서울신문(뉴 MINI 클럽맨 2015.11.20 국내 출시)</t>
         </is>
       </c>
       <c r="P63" s="9" t="inlineStr"/>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="O64" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 서울신문(뉴 MINI 클럽맨 2015.11.20 국내 출시)</t>
         </is>
       </c>
       <c r="P64" s="9" t="inlineStr"/>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="O65" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 서울신문(뉴 MINI 클럽맨 2015.11.20 국내 출시)</t>
         </is>
       </c>
       <c r="P65" s="9" t="inlineStr"/>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024(단종)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="O66" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 서울신문(뉴 MINI 클럽맨 2015.11.20 국내 출시)</t>
         </is>
       </c>
       <c r="P66" s="9" t="inlineStr"/>
@@ -5150,22 +5150,22 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>클럽맨 (F54, 3세대)</t>
+          <t>페이스맨 (R61)</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>ID49(PCF7953P)</t>
+          <t>ID46(PCF7945)</t>
         </is>
       </c>
       <c r="H67" s="9" t="inlineStr">
@@ -5185,29 +5185,29 @@
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>51217359252[비상키, 해외 공용 품번]</t>
+          <t>51212756065[비상키, 해외 공용 품번], 51212756061[비상키, 해외 공용 품번], 66123456377[트랜스폰더 키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
-          <t>HU100R</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K67" s="9" t="inlineStr"/>
       <c r="L67" s="9" t="inlineStr">
         <is>
-          <t>66128781934, 66128728017[컴포트 액세스]</t>
+          <t>66123456369, 66123456373[컴포트 액세스]</t>
         </is>
       </c>
       <c r="M67" s="9" t="inlineStr"/>
       <c r="N67" s="9" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>CAS3, CAS3+</t>
         </is>
       </c>
       <c r="O67" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI R61 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), 이데일리(페이스맨 2013년 상반기 국내 판매)</t>
         </is>
       </c>
       <c r="P67" s="9" t="inlineStr"/>
@@ -5220,22 +5220,22 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>클럽맨 (F54, 3세대)</t>
+          <t>페이스맨 (R61)</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>2024(단종)</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>ID49(PCF7953P)</t>
+          <t>ID46(PCF7945)</t>
         </is>
       </c>
       <c r="H68" s="9" t="inlineStr">
@@ -5255,29 +5255,29 @@
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>51217359252[비상키, 해외 공용 품번]</t>
+          <t>51212756065[비상키, 해외 공용 품번], 51212756061[비상키, 해외 공용 품번], 66123456377[트랜스폰더 키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>HU100R</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K68" s="9" t="inlineStr"/>
       <c r="L68" s="9" t="inlineStr">
         <is>
-          <t>66128781934, 66128728017[컴포트 액세스]</t>
+          <t>66123456369, 66123456373[컴포트 액세스]</t>
         </is>
       </c>
       <c r="M68" s="9" t="inlineStr"/>
       <c r="N68" s="9" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>CAS3, CAS3+</t>
         </is>
       </c>
       <c r="O68" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F54 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI R61 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), 이데일리(페이스맨 2013년 상반기 국내 판매)</t>
         </is>
       </c>
       <c r="P68" s="9" t="inlineStr"/>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="O69" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R61 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI R61 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), 이데일리(페이스맨 2013년 상반기 국내 판매)</t>
         </is>
       </c>
       <c r="P69" s="9" t="inlineStr"/>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2016(단종)</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O70" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R61 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI R61 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), 이데일리(페이스맨 2013년 상반기 국내 판매)</t>
         </is>
       </c>
       <c r="P70" s="9" t="inlineStr"/>
@@ -5430,12 +5430,12 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>페이스맨 (R61)</t>
+          <t>컨트리맨 (R60, 1세대)</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="O71" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R61 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI R60 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님, 트랜스폰더 키 66123456377은 2011.3 생산까지), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), BMW 프레스(MINI 컨트리맨 2011.3 국내 출시)</t>
         </is>
       </c>
       <c r="P71" s="9" t="inlineStr"/>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>페이스맨 (R61)</t>
+          <t>컨트리맨 (R60, 1세대)</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>2016(단종)</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
-          <t>51212756065[비상키, 해외 공용 품번], 51212756061[비상키, 해외 공용 품번], 66123456377[트랜스폰더 키, 해외 공용 품번]</t>
+          <t>51212756061[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J72" s="9" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="O72" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R61 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI R60 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 비상키 51212756061 — 트랜스폰더 키 66123456377·비상키 51212756065는 2011.3 생산까지), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
         </is>
       </c>
       <c r="P72" s="9" t="inlineStr"/>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>51212756065[비상키, 해외 공용 품번], 51212756061[비상키, 해외 공용 품번], 66123456377[트랜스폰더 키, 해외 공용 품번]</t>
+          <t>51212756061[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J73" s="9" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O73" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R60 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 국가 제한 없는 비상키 51212756065·51212756061·트랜스폰더 키 66123456377 — 434MHz 66123456370·868MHz 66123456367은 한국 사양 아님, 트랜스폰더 키 66123456377은 2011.3 생산까지), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+), BMW 프레스(MINI 컨트리맨 2011.3 국내 출시)</t>
+          <t>BMW ETK(MINI R60 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 비상키 51212756061 — 트랜스폰더 키 66123456377·비상키 51212756065는 2011.3 생산까지), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
         </is>
       </c>
       <c r="P73" s="9" t="inlineStr"/>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2016(단종)</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -5850,22 +5850,22 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>컨트리맨 (R60, 1세대)</t>
+          <t>컨트리맨 (F60, 2세대)</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>ID46(PCF7945)</t>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H77" s="9" t="inlineStr">
@@ -5885,29 +5885,29 @@
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>51212756061[비상키, 해외 공용 품번]</t>
+          <t>51217359252[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J77" s="9" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K77" s="9" t="inlineStr"/>
       <c r="L77" s="9" t="inlineStr">
         <is>
-          <t>66123456369, 66123456373[컴포트 액세스]</t>
+          <t>66128781934</t>
         </is>
       </c>
       <c r="M77" s="9" t="inlineStr"/>
       <c r="N77" s="9" t="inlineStr">
         <is>
-          <t>CAS3, CAS3+</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O77" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R60 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 비상키 51212756061 — 트랜스폰더 키 66123456377·비상키 51212756065는 2011.3 생산까지), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI F60 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 이데일리(2세대 컨트리맨 2017 서울모터쇼 국내 공개·출시)</t>
         </is>
       </c>
       <c r="P77" s="9" t="inlineStr"/>
@@ -5920,22 +5920,22 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>컨트리맨 (R60, 1세대)</t>
+          <t>컨트리맨 (F60, 2세대)</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>2016(단종)</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>ID46(PCF7945)</t>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H78" s="9" t="inlineStr">
@@ -5955,29 +5955,29 @@
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
-          <t>51212756061[비상키, 해외 공용 품번]</t>
+          <t>51217359252[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K78" s="9" t="inlineStr"/>
       <c r="L78" s="9" t="inlineStr">
         <is>
-          <t>66123456369, 66123456373[컴포트 액세스]</t>
+          <t>66128781934</t>
         </is>
       </c>
       <c r="M78" s="9" t="inlineStr"/>
       <c r="N78" s="9" t="inlineStr">
         <is>
-          <t>CAS3, CAS3+</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O78" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI R60 키 부품: 한국 사양 L802A 리모컨 66123456369(315MHZ LP)·컴포트 액세스 66123456373(315MHZ LP), 비상키 51212756061 — 트랜스폰더 키 66123456377·비상키 51212756065는 2011.3 생산까지), transpondery(BMW Catalog MINI Cooper 2006–2012 Philips Crypto 2 ID46 PCF7945, CAS3·CAS3+)</t>
+          <t>BMW ETK(MINI F60 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 이데일리(2세대 컨트리맨 2017 서울모터쇼 국내 공개·출시)</t>
         </is>
       </c>
       <c r="P78" s="9" t="inlineStr"/>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -6036,7 +6036,7 @@
       <c r="K79" s="9" t="inlineStr"/>
       <c r="L79" s="9" t="inlineStr">
         <is>
-          <t>66128781934</t>
+          <t>66128781934, 66128728017[컴포트 액세스]</t>
         </is>
       </c>
       <c r="M79" s="9" t="inlineStr"/>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="O79" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F60 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F60 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 이데일리(2세대 컨트리맨 2017 서울모터쇼 국내 공개·출시)</t>
         </is>
       </c>
       <c r="P79" s="9" t="inlineStr"/>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -6106,7 +6106,7 @@
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr">
         <is>
-          <t>66128781934</t>
+          <t>66128781934, 66128728017[컴포트 액세스]</t>
         </is>
       </c>
       <c r="M80" s="9" t="inlineStr"/>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="O80" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F60 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F60 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 이데일리(2세대 컨트리맨 2017 서울모터쇼 국내 공개·출시)</t>
         </is>
       </c>
       <c r="P80" s="9" t="inlineStr"/>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="O81" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F60 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F60 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 이데일리(2세대 컨트리맨 2017 서울모터쇼 국내 공개·출시)</t>
         </is>
       </c>
       <c r="P81" s="9" t="inlineStr"/>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="O82" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F60 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F60 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 이데일리(2세대 컨트리맨 2017 서울모터쇼 국내 공개·출시)</t>
         </is>
       </c>
       <c r="P82" s="9" t="inlineStr"/>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023(단종)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="O83" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F60 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
+          <t>BMW ETK(MINI F60 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC), 이데일리(2세대 컨트리맨 2017 서울모터쇼 국내 공개·출시)</t>
         </is>
       </c>
       <c r="P83" s="9" t="inlineStr"/>
@@ -6340,12 +6340,12 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>컨트리맨 (F60, 2세대)</t>
+          <t>컨트리맨 (U25, 3세대)</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -6363,9 +6363,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G84" s="9" t="inlineStr">
-        <is>
-          <t>ID49(PCF7953P)</t>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H84" s="9" t="inlineStr">
@@ -6373,34 +6373,26 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>51217359252[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I84" s="9" t="inlineStr"/>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>HU100R</t>
+          <t>HU100R[추정]</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr"/>
-      <c r="L84" s="9" t="inlineStr">
-        <is>
-          <t>66128781934, 66128728017[컴포트 액세스]</t>
-        </is>
-      </c>
+      <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
-      <c r="N84" s="9" t="inlineStr">
-        <is>
-          <t>BDC</t>
-        </is>
-      </c>
+      <c r="N84" s="9" t="inlineStr"/>
       <c r="O84" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F60 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
-        </is>
-      </c>
-      <c r="P84" s="9" t="inlineStr"/>
+          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 목록(2024-현재)</t>
+        </is>
+      </c>
+      <c r="P84" s="6" t="inlineStr">
+        <is>
+          <t>2024년 이후 신형 MINI 칩 자료 없음 — 같은 시기 BMW(ID49) 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
@@ -6410,12 +6402,12 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>컨트리맨 (F60, 2세대)</t>
+          <t>컨트리맨 (U25, 3세대)</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>2023(단종)</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -6433,9 +6425,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G85" s="9" t="inlineStr">
-        <is>
-          <t>ID49(PCF7953P)</t>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H85" s="9" t="inlineStr">
@@ -6443,34 +6435,26 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>51217359252[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I85" s="9" t="inlineStr"/>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>HU100R</t>
+          <t>HU100R[추정]</t>
         </is>
       </c>
       <c r="K85" s="9" t="inlineStr"/>
-      <c r="L85" s="9" t="inlineStr">
-        <is>
-          <t>66128781934, 66128728017[컴포트 액세스]</t>
-        </is>
-      </c>
+      <c r="L85" s="9" t="inlineStr"/>
       <c r="M85" s="9" t="inlineStr"/>
-      <c r="N85" s="9" t="inlineStr">
-        <is>
-          <t>BDC</t>
-        </is>
-      </c>
+      <c r="N85" s="9" t="inlineStr"/>
       <c r="O85" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK(MINI F60 키 부품: 한국 사양 L802A 리모컨 66128781934(434 MHZ KO), 2019.3 이후 컴포트 액세스 66128728017(434 MHZ KO CA), 비상키 51217359252 — 66128781935(434MHz 국가 제한 없음)·66128781936(315MHz)은 한국 사양 아님), transpondery(BMW Catalog MINI Cooper 2013+ Philips Crypto 3 Hitag Pro PCF7953 ID49, BDC)</t>
-        </is>
-      </c>
-      <c r="P85" s="9" t="inlineStr"/>
+          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 목록(2024-현재)</t>
+        </is>
+      </c>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t>2024년 이후 신형 MINI 칩 자료 없음 — 같은 시기 BMW(ID49) 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
@@ -6485,7 +6469,7 @@
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -6542,7 +6526,7 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>컨트리맨 (U25, 3세대)</t>
+          <t>에이스맨 (신형, 전기차)</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
@@ -6587,7 +6571,7 @@
       <c r="N87" s="9" t="inlineStr"/>
       <c r="O87" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 목록(2024-현재)</t>
+          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 헤럴드경제·ZDNet(더 뉴 올-일렉트릭 MINI 에이스맨 2025.3 국내 출시)</t>
         </is>
       </c>
       <c r="P87" s="6" t="inlineStr">
@@ -6604,7 +6588,7 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>컨트리맨 (U25, 3세대)</t>
+          <t>에이스맨 (신형, 전기차)</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
@@ -6649,7 +6633,7 @@
       <c r="N88" s="9" t="inlineStr"/>
       <c r="O88" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 목록(2024-현재)</t>
+          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 헤럴드경제·ZDNet(더 뉴 올-일렉트릭 MINI 에이스맨 2025.3 국내 출시)</t>
         </is>
       </c>
       <c r="P88" s="6" t="inlineStr">
@@ -6658,132 +6642,8 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="9" t="inlineStr">
-        <is>
-          <t>MINI</t>
-        </is>
-      </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t>에이스맨 (신형, 전기차)</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H89" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I89" s="9" t="inlineStr"/>
-      <c r="J89" s="9" t="inlineStr">
-        <is>
-          <t>HU100R[추정]</t>
-        </is>
-      </c>
-      <c r="K89" s="9" t="inlineStr"/>
-      <c r="L89" s="9" t="inlineStr"/>
-      <c r="M89" s="9" t="inlineStr"/>
-      <c r="N89" s="9" t="inlineStr"/>
-      <c r="O89" s="9" t="inlineStr">
-        <is>
-          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 헤럴드경제·ZDNet(더 뉴 올-일렉트릭 MINI 에이스맨 2025.3 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P89" s="6" t="inlineStr">
-        <is>
-          <t>2024년 이후 신형 MINI 칩 자료 없음 — 같은 시기 BMW(ID49) 기준 추정</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="9" t="inlineStr">
-        <is>
-          <t>MINI</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>에이스맨 (신형, 전기차)</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H90" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I90" s="9" t="inlineStr"/>
-      <c r="J90" s="9" t="inlineStr">
-        <is>
-          <t>HU100R[추정]</t>
-        </is>
-      </c>
-      <c r="K90" s="9" t="inlineStr"/>
-      <c r="L90" s="9" t="inlineStr"/>
-      <c r="M90" s="9" t="inlineStr"/>
-      <c r="N90" s="9" t="inlineStr"/>
-      <c r="O90" s="9" t="inlineStr">
-        <is>
-          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 헤럴드경제·ZDNet(더 뉴 올-일렉트릭 MINI 에이스맨 2025.3 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P90" s="6" t="inlineStr">
-        <is>
-          <t>2024년 이후 신형 MINI 칩 자료 없음 — 같은 시기 BMW(ID49) 기준 추정</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P90"/>
+  <autoFilter ref="A1:P88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6941,7 +6801,7 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>- 쿠퍼 해치백 R56: 2007년 국내 출시 → 2007~2014 / 쿠퍼 일렉트릭(쿠퍼 SE): 2022.2.28 국내 출시 → 2022~2024 / 컨트리맨 R60: 2011.3 국내 출시 → 2011~2016 / 에이스맨: 2025.3 국내 출시 → 2025~.</t>
+          <t>- 쿠퍼 해치백 R56: 2007년 국내 출시 → 2007~2014 / 쿠퍼 일렉트릭(쿠퍼 SE): 2022.2.28 국내 출시 → 2022~2024 / 컨트리맨 R60: 2011.3 국내 출시 → 2011~2016 / 에이스맨: 2025.3 국내 출시 → 2025~ / 클럽맨 R55: 2008.2.26 국내 첫 출시 → 2008~2015 / 컨버터블 F57: 2016.4 국내 출시 → 2016~2024.</t>
         </is>
       </c>
     </row>

--- a/MINI_models.xlsx
+++ b/MINI_models.xlsx
@@ -2346,10 +2346,14 @@
       <c r="K26" s="9" t="inlineStr"/>
       <c r="L26" s="9" t="inlineStr"/>
       <c r="M26" s="9" t="inlineStr"/>
-      <c r="N26" s="9" t="inlineStr"/>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>BCP[추정]</t>
+        </is>
+      </c>
       <c r="O26" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 아주경제·BMW 프레스(뉴 MINI 쿠퍼 3-도어 2024, 5-도어 2024.10.8 국내 출시)</t>
+          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·BCP·HU100R 기준 추정, 아주경제·BMW 프레스(뉴 MINI 쿠퍼 3-도어 2024, 5-도어 2024.10.8 국내 출시)</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
@@ -2408,10 +2412,14 @@
       <c r="K27" s="9" t="inlineStr"/>
       <c r="L27" s="9" t="inlineStr"/>
       <c r="M27" s="9" t="inlineStr"/>
-      <c r="N27" s="9" t="inlineStr"/>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>BCP[추정]</t>
+        </is>
+      </c>
       <c r="O27" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 아주경제·BMW 프레스(뉴 MINI 쿠퍼 3-도어 2024, 5-도어 2024.10.8 국내 출시)</t>
+          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·BCP·HU100R 기준 추정, 아주경제·BMW 프레스(뉴 MINI 쿠퍼 3-도어 2024, 5-도어 2024.10.8 국내 출시)</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
@@ -2470,10 +2478,14 @@
       <c r="K28" s="9" t="inlineStr"/>
       <c r="L28" s="9" t="inlineStr"/>
       <c r="M28" s="9" t="inlineStr"/>
-      <c r="N28" s="9" t="inlineStr"/>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>BCP[추정]</t>
+        </is>
+      </c>
       <c r="O28" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 아주경제·BMW 프레스(뉴 MINI 쿠퍼 3-도어 2024, 5-도어 2024.10.8 국내 출시)</t>
+          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·BCP·HU100R 기준 추정, 아주경제·BMW 프레스(뉴 MINI 쿠퍼 3-도어 2024, 5-도어 2024.10.8 국내 출시)</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
@@ -6382,10 +6394,14 @@
       <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
-      <c r="N84" s="9" t="inlineStr"/>
+      <c r="N84" s="6" t="inlineStr">
+        <is>
+          <t>BCP[추정]</t>
+        </is>
+      </c>
       <c r="O84" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 목록(2024-현재)</t>
+          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·BCP·HU100R 기준 추정, 목록(2024-현재)</t>
         </is>
       </c>
       <c r="P84" s="6" t="inlineStr">
@@ -6444,10 +6460,14 @@
       <c r="K85" s="9" t="inlineStr"/>
       <c r="L85" s="9" t="inlineStr"/>
       <c r="M85" s="9" t="inlineStr"/>
-      <c r="N85" s="9" t="inlineStr"/>
+      <c r="N85" s="6" t="inlineStr">
+        <is>
+          <t>BCP[추정]</t>
+        </is>
+      </c>
       <c r="O85" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 목록(2024-현재)</t>
+          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·BCP·HU100R 기준 추정, 목록(2024-현재)</t>
         </is>
       </c>
       <c r="P85" s="6" t="inlineStr">
@@ -6506,10 +6526,14 @@
       <c r="K86" s="9" t="inlineStr"/>
       <c r="L86" s="9" t="inlineStr"/>
       <c r="M86" s="9" t="inlineStr"/>
-      <c r="N86" s="9" t="inlineStr"/>
+      <c r="N86" s="6" t="inlineStr">
+        <is>
+          <t>BCP[추정]</t>
+        </is>
+      </c>
       <c r="O86" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 목록(2024-현재)</t>
+          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·BCP·HU100R 기준 추정, 목록(2024-현재)</t>
         </is>
       </c>
       <c r="P86" s="6" t="inlineStr">
@@ -6568,10 +6592,14 @@
       <c r="K87" s="9" t="inlineStr"/>
       <c r="L87" s="9" t="inlineStr"/>
       <c r="M87" s="9" t="inlineStr"/>
-      <c r="N87" s="9" t="inlineStr"/>
+      <c r="N87" s="6" t="inlineStr">
+        <is>
+          <t>BCP[추정]</t>
+        </is>
+      </c>
       <c r="O87" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 헤럴드경제·ZDNet(더 뉴 올-일렉트릭 MINI 에이스맨 2025.3 국내 출시)</t>
+          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·BCP·HU100R 기준 추정, 헤럴드경제·ZDNet(더 뉴 올-일렉트릭 MINI 에이스맨 2025.3 국내 출시)</t>
         </is>
       </c>
       <c r="P87" s="6" t="inlineStr">
@@ -6630,10 +6658,14 @@
       <c r="K88" s="9" t="inlineStr"/>
       <c r="L88" s="9" t="inlineStr"/>
       <c r="M88" s="9" t="inlineStr"/>
-      <c r="N88" s="9" t="inlineStr"/>
+      <c r="N88" s="6" t="inlineStr">
+        <is>
+          <t>BCP[추정]</t>
+        </is>
+      </c>
       <c r="O88" s="9" t="inlineStr">
         <is>
-          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·HU100R 기준 추정, 헤럴드경제·ZDNet(더 뉴 올-일렉트릭 MINI 에이스맨 2025.3 국내 출시)</t>
+          <t>BMW ETK 03.2019판에 2024년 이후 신형 미수록, transpondery MINI는 2013+ ID49까지만 — 같은 세대 BMW U11(X1) ID49·BCP·HU100R 기준 추정, 헤럴드경제·ZDNet(더 뉴 올-일렉트릭 MINI 에이스맨 2025.3 국내 출시)</t>
         </is>
       </c>
       <c r="P88" s="6" t="inlineStr">
